--- a/operator/public/file/Products_template.xlsx
+++ b/operator/public/file/Products_template.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-15" yWindow="-15" windowWidth="20670" windowHeight="12585"/>
+    <workbookView windowWidth="28800" windowHeight="12240"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
-  <fileRecoveryPr repairLoad="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -28,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
     <t>Id</t>
   </si>
@@ -51,6 +50,30 @@
     <t>Subcategory_id</t>
   </si>
   <si>
+    <t>Is Variant</t>
+  </si>
+  <si>
+    <t>Product label</t>
+  </si>
+  <si>
+    <t>Product Price</t>
+  </si>
+  <si>
+    <t>Discount type</t>
+  </si>
+  <si>
+    <t>Discount Value</t>
+  </si>
+  <si>
+    <t>Stock</t>
+  </si>
+  <si>
+    <t>SKU Code</t>
+  </si>
+  <si>
+    <t>HSN Code</t>
+  </si>
+  <si>
     <t>Product_type</t>
   </si>
   <si>
@@ -85,34 +108,19 @@
   </si>
   <si>
     <t>Shipping_policy</t>
-  </si>
-  <si>
-    <t>Discount Value</t>
-  </si>
-  <si>
-    <t>Discount type</t>
-  </si>
-  <si>
-    <t>Product label</t>
-  </si>
-  <si>
-    <t>Product Price</t>
-  </si>
-  <si>
-    <t>Stock</t>
-  </si>
-  <si>
-    <t>SKU Code</t>
-  </si>
-  <si>
-    <t>HSN Code</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="10">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -149,42 +157,186 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF444444"/>
-      <name val="Calibri"/>
+      <name val="Consolas"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF444444"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="Consolas"/>
-      <family val="3"/>
-    </font>
-    <font>
-      <sz val="12"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -197,8 +349,194 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -206,9 +544,251 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -233,175 +813,106 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="22" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="22" fontId="9" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
   <dxfs count="17">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
+        <b val="1"/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="1"/>
       </font>
       <border>
@@ -412,7 +923,7 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="0"/>
       </font>
       <fill>
@@ -440,32 +951,149 @@
           <color theme="4"/>
         </bottom>
         <horizontal style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
+          <color theme="4" tint="0.399975585192419"/>
         </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
       </border>
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
-    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7">
-      <tableStyleElement type="wholeTable" dxfId="16"/>
-      <tableStyleElement type="headerRow" dxfId="15"/>
-      <tableStyleElement type="totalRow" dxfId="14"/>
-      <tableStyleElement type="firstColumn" dxfId="13"/>
-      <tableStyleElement type="lastColumn" dxfId="12"/>
-      <tableStyleElement type="firstRowStripe" dxfId="11"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="10"/>
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+      <tableStyleElement type="wholeTable" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="totalRow" dxfId="4"/>
+      <tableStyleElement type="firstColumn" dxfId="3"/>
+      <tableStyleElement type="lastColumn" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
     </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10">
-      <tableStyleElement type="headerRow" dxfId="9"/>
-      <tableStyleElement type="totalRow" dxfId="8"/>
-      <tableStyleElement type="firstRowStripe" dxfId="7"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="6"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="5"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="4"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="3"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="2"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="1"/>
-      <tableStyleElement type="pageFieldValues" dxfId="0"/>
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
+      <tableStyleElement type="pageFieldValues" dxfId="7"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -477,7 +1105,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
@@ -499,7 +1127,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" r:link="rId2"/>
+        <a:blip r:embed="rId1" r:link="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -541,7 +1169,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" r:link="rId2"/>
+        <a:blip r:embed="rId3" r:link="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -560,6 +1188,36 @@
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1028" name="Host Control  4"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="2971800"/>
+          <a:ext cx="7620" cy="198120"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -817,39 +1475,39 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AI114"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:AJ114"/>
+  <sheetFormatPr defaultColWidth="8.85185185185185" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="29.28515625" customWidth="1"/>
-    <col min="2" max="2" width="37.140625" customWidth="1"/>
-    <col min="3" max="3" width="16.28515625" customWidth="1"/>
-    <col min="4" max="4" width="33.5703125" customWidth="1"/>
-    <col min="5" max="5" width="40.7109375" customWidth="1"/>
+    <col min="1" max="1" width="29.287037037037" customWidth="1"/>
+    <col min="2" max="2" width="37.1388888888889" customWidth="1"/>
+    <col min="3" max="3" width="16.287037037037" customWidth="1"/>
+    <col min="4" max="4" width="33.5740740740741" customWidth="1"/>
+    <col min="5" max="5" width="40.712962962963" customWidth="1"/>
     <col min="6" max="6" width="52" customWidth="1"/>
-    <col min="7" max="11" width="18.7109375" customWidth="1"/>
-    <col min="13" max="14" width="18.7109375" customWidth="1"/>
-    <col min="15" max="15" width="25.7109375" customWidth="1"/>
-    <col min="16" max="16" width="42.28515625" customWidth="1"/>
-    <col min="17" max="17" width="15.140625" customWidth="1"/>
-    <col min="18" max="18" width="15.85546875" customWidth="1"/>
-    <col min="19" max="19" width="19.42578125" customWidth="1"/>
-    <col min="20" max="20" width="17.140625" customWidth="1"/>
-    <col min="21" max="21" width="17.7109375" customWidth="1"/>
-    <col min="22" max="22" width="36.140625" customWidth="1"/>
-    <col min="23" max="23" width="49.28515625" customWidth="1"/>
-    <col min="24" max="24" width="16.140625" customWidth="1"/>
-    <col min="25" max="25" width="16.42578125" customWidth="1"/>
-    <col min="26" max="26" width="15.28515625" customWidth="1"/>
-    <col min="28" max="28" width="16.7109375" customWidth="1"/>
+    <col min="7" max="12" width="18.712962962963" customWidth="1"/>
+    <col min="14" max="15" width="18.712962962963" customWidth="1"/>
+    <col min="16" max="16" width="25.712962962963" customWidth="1"/>
+    <col min="17" max="17" width="42.287037037037" customWidth="1"/>
+    <col min="18" max="18" width="15.1388888888889" customWidth="1"/>
+    <col min="19" max="19" width="15.8518518518519" customWidth="1"/>
+    <col min="20" max="20" width="19.4259259259259" customWidth="1"/>
+    <col min="21" max="21" width="17.1388888888889" customWidth="1"/>
+    <col min="22" max="22" width="17.712962962963" customWidth="1"/>
+    <col min="23" max="23" width="36.1388888888889" customWidth="1"/>
+    <col min="24" max="24" width="49.287037037037" customWidth="1"/>
+    <col min="25" max="25" width="16.1388888888889" customWidth="1"/>
+    <col min="26" max="26" width="16.4259259259259" customWidth="1"/>
+    <col min="27" max="27" width="15.287037037037" customWidth="1"/>
+    <col min="29" max="29" width="16.712962962963" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" s="1" customFormat="1" ht="15.6" customHeight="1">
+    <row r="1" s="1" customFormat="1" ht="15.6" customHeight="1" spans="1:36">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -871,74 +1529,77 @@
       <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="11" t="s">
+      <c r="H1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="I1" s="11" t="s">
+      <c r="W1" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="J1" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="K1" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="L1" s="12" t="s">
+      <c r="X1" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="M1" s="11" t="s">
+      <c r="Y1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="N1" s="11" t="s">
+      <c r="Z1" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="O1" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q1" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="R1" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="S1" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="T1" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="U1" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="V1" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="W1" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="X1" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y1" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="Z1" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="AA1" s="3"/>
-      <c r="AB1" s="2"/>
-      <c r="AC1" s="3"/>
-      <c r="AD1" s="4"/>
-      <c r="AE1" s="3"/>
-      <c r="AF1" s="2"/>
-      <c r="AG1" s="3"/>
-      <c r="AH1" s="4"/>
-      <c r="AI1" s="3"/>
-    </row>
-    <row r="2" spans="1:35" ht="15.75">
+      <c r="AA1" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="3"/>
+      <c r="AC1" s="2"/>
+      <c r="AD1" s="3"/>
+      <c r="AE1" s="4"/>
+      <c r="AF1" s="3"/>
+      <c r="AG1" s="2"/>
+      <c r="AH1" s="3"/>
+      <c r="AI1" s="4"/>
+      <c r="AJ1" s="3"/>
+    </row>
+    <row r="2" ht="15.6" spans="1:22">
       <c r="A2" s="5"/>
       <c r="B2" s="6"/>
       <c r="C2" s="7"/>
@@ -946,20 +1607,21 @@
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
       <c r="G2" s="6"/>
-      <c r="H2" s="13"/>
-      <c r="I2" s="6"/>
+      <c r="H2" s="8"/>
+      <c r="I2" s="8"/>
       <c r="J2" s="6"/>
       <c r="K2" s="6"/>
-      <c r="L2" s="13"/>
-      <c r="M2" s="13"/>
-      <c r="N2" s="13"/>
-      <c r="O2" s="6"/>
-      <c r="R2" s="6"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="8"/>
+      <c r="N2" s="8"/>
+      <c r="O2" s="8"/>
+      <c r="P2" s="6"/>
       <c r="S2" s="6"/>
       <c r="T2" s="6"/>
       <c r="U2" s="6"/>
-    </row>
-    <row r="3" spans="1:35" ht="15.75">
+      <c r="V2" s="6"/>
+    </row>
+    <row r="3" ht="15.6" spans="1:16">
       <c r="A3" s="5"/>
       <c r="B3" s="6"/>
       <c r="C3" s="7"/>
@@ -971,11 +1633,12 @@
       <c r="I3" s="6"/>
       <c r="J3" s="6"/>
       <c r="K3" s="6"/>
-      <c r="M3" s="6"/>
+      <c r="L3" s="6"/>
       <c r="N3" s="6"/>
       <c r="O3" s="6"/>
-    </row>
-    <row r="4" spans="1:35" ht="15.75">
+      <c r="P3" s="6"/>
+    </row>
+    <row r="4" ht="15.6" spans="1:17">
       <c r="A4" s="6"/>
       <c r="B4" s="6"/>
       <c r="C4" s="7"/>
@@ -987,12 +1650,13 @@
       <c r="I4" s="6"/>
       <c r="J4" s="6"/>
       <c r="K4" s="6"/>
-      <c r="M4" s="6"/>
+      <c r="L4" s="6"/>
       <c r="N4" s="6"/>
       <c r="O4" s="6"/>
       <c r="P4" s="6"/>
-    </row>
-    <row r="5" spans="1:35" ht="15.75">
+      <c r="Q4" s="6"/>
+    </row>
+    <row r="5" ht="15.6" spans="1:17">
       <c r="A5" s="6"/>
       <c r="B5" s="6"/>
       <c r="C5" s="7"/>
@@ -1004,12 +1668,13 @@
       <c r="I5" s="6"/>
       <c r="J5" s="6"/>
       <c r="K5" s="6"/>
-      <c r="M5" s="6"/>
+      <c r="L5" s="6"/>
       <c r="N5" s="6"/>
       <c r="O5" s="6"/>
       <c r="P5" s="6"/>
-    </row>
-    <row r="6" spans="1:35" ht="15.75">
+      <c r="Q5" s="6"/>
+    </row>
+    <row r="6" ht="15.6" spans="1:23">
       <c r="A6" s="6"/>
       <c r="B6" s="6"/>
       <c r="C6" s="7"/>
@@ -1021,13 +1686,14 @@
       <c r="I6" s="6"/>
       <c r="J6" s="6"/>
       <c r="K6" s="6"/>
-      <c r="M6" s="6"/>
+      <c r="L6" s="6"/>
       <c r="N6" s="6"/>
       <c r="O6" s="6"/>
       <c r="P6" s="6"/>
-      <c r="V6" s="7"/>
-    </row>
-    <row r="7" spans="1:35" ht="15.75">
+      <c r="Q6" s="6"/>
+      <c r="W6" s="7"/>
+    </row>
+    <row r="7" ht="15.6" spans="1:28">
       <c r="A7" s="6"/>
       <c r="B7" s="6"/>
       <c r="C7" s="7"/>
@@ -1039,14 +1705,15 @@
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
       <c r="K7" s="6"/>
-      <c r="M7" s="6"/>
+      <c r="L7" s="6"/>
       <c r="N7" s="6"/>
       <c r="O7" s="6"/>
       <c r="P7" s="6"/>
-      <c r="V7" s="7"/>
-      <c r="AA7" s="6"/>
-    </row>
-    <row r="8" spans="1:35" ht="15.75">
+      <c r="Q7" s="6"/>
+      <c r="W7" s="7"/>
+      <c r="AB7" s="6"/>
+    </row>
+    <row r="8" ht="15.6" spans="1:23">
       <c r="A8" s="6"/>
       <c r="B8" s="6"/>
       <c r="C8" s="7"/>
@@ -1058,13 +1725,14 @@
       <c r="I8" s="6"/>
       <c r="J8" s="6"/>
       <c r="K8" s="6"/>
-      <c r="M8" s="6"/>
+      <c r="L8" s="6"/>
       <c r="N8" s="6"/>
       <c r="O8" s="6"/>
       <c r="P8" s="6"/>
-      <c r="V8" s="7"/>
-    </row>
-    <row r="9" spans="1:35" ht="15.75">
+      <c r="Q8" s="6"/>
+      <c r="W8" s="7"/>
+    </row>
+    <row r="9" ht="15.6" spans="1:23">
       <c r="A9" s="6"/>
       <c r="B9" s="6"/>
       <c r="C9" s="7"/>
@@ -1076,13 +1744,14 @@
       <c r="I9" s="6"/>
       <c r="J9" s="6"/>
       <c r="K9" s="6"/>
-      <c r="M9" s="6"/>
+      <c r="L9" s="6"/>
       <c r="N9" s="6"/>
       <c r="O9" s="6"/>
       <c r="P9" s="6"/>
-      <c r="V9" s="7"/>
-    </row>
-    <row r="10" spans="1:35" ht="15.75">
+      <c r="Q9" s="6"/>
+      <c r="W9" s="7"/>
+    </row>
+    <row r="10" ht="15.6" spans="1:29">
       <c r="A10" s="6"/>
       <c r="B10" s="6"/>
       <c r="C10" s="7"/>
@@ -1094,14 +1763,15 @@
       <c r="I10" s="6"/>
       <c r="J10" s="6"/>
       <c r="K10" s="6"/>
-      <c r="M10" s="6"/>
+      <c r="L10" s="6"/>
       <c r="N10" s="6"/>
       <c r="O10" s="6"/>
       <c r="P10" s="6"/>
-      <c r="V10" s="7"/>
-      <c r="AB10" s="6"/>
-    </row>
-    <row r="11" spans="1:35" ht="15.75">
+      <c r="Q10" s="6"/>
+      <c r="W10" s="7"/>
+      <c r="AC10" s="6"/>
+    </row>
+    <row r="11" ht="15.6" spans="1:29">
       <c r="A11" s="6"/>
       <c r="B11" s="6"/>
       <c r="C11" s="7"/>
@@ -1113,14 +1783,15 @@
       <c r="I11" s="6"/>
       <c r="J11" s="6"/>
       <c r="K11" s="6"/>
-      <c r="M11" s="6"/>
+      <c r="L11" s="6"/>
       <c r="N11" s="6"/>
       <c r="O11" s="6"/>
       <c r="P11" s="6"/>
-      <c r="V11" s="7"/>
-      <c r="AB11" s="6"/>
-    </row>
-    <row r="12" spans="1:35" ht="15.75">
+      <c r="Q11" s="6"/>
+      <c r="W11" s="7"/>
+      <c r="AC11" s="6"/>
+    </row>
+    <row r="12" ht="15.6" spans="1:29">
       <c r="A12" s="6"/>
       <c r="B12" s="6"/>
       <c r="C12" s="7"/>
@@ -1132,14 +1803,15 @@
       <c r="I12" s="6"/>
       <c r="J12" s="6"/>
       <c r="K12" s="6"/>
-      <c r="M12" s="6"/>
+      <c r="L12" s="6"/>
       <c r="N12" s="6"/>
       <c r="O12" s="6"/>
       <c r="P12" s="6"/>
-      <c r="V12" s="7"/>
-      <c r="AB12" s="6"/>
-    </row>
-    <row r="13" spans="1:35" ht="15.75">
+      <c r="Q12" s="6"/>
+      <c r="W12" s="7"/>
+      <c r="AC12" s="6"/>
+    </row>
+    <row r="13" ht="15.6" spans="1:29">
       <c r="A13" s="6"/>
       <c r="B13" s="6"/>
       <c r="C13" s="7"/>
@@ -1151,15 +1823,16 @@
       <c r="I13" s="6"/>
       <c r="J13" s="6"/>
       <c r="K13" s="6"/>
-      <c r="M13" s="6"/>
+      <c r="L13" s="6"/>
       <c r="N13" s="6"/>
       <c r="O13" s="6"/>
       <c r="P13" s="6"/>
-      <c r="V13" s="7"/>
-      <c r="AA13" s="6"/>
+      <c r="Q13" s="6"/>
+      <c r="W13" s="7"/>
       <c r="AB13" s="6"/>
-    </row>
-    <row r="14" spans="1:35" ht="15.75">
+      <c r="AC13" s="6"/>
+    </row>
+    <row r="14" ht="15.6" spans="1:31">
       <c r="A14" s="6"/>
       <c r="B14" s="6"/>
       <c r="C14" s="7"/>
@@ -1171,16 +1844,17 @@
       <c r="I14" s="6"/>
       <c r="J14" s="6"/>
       <c r="K14" s="6"/>
-      <c r="M14" s="6"/>
+      <c r="L14" s="6"/>
       <c r="N14" s="6"/>
       <c r="O14" s="6"/>
       <c r="P14" s="6"/>
-      <c r="V14" s="7"/>
-      <c r="AB14" s="6"/>
-      <c r="AC14" s="8"/>
-      <c r="AD14" s="9"/>
-    </row>
-    <row r="15" spans="1:35" ht="15.75">
+      <c r="Q14" s="6"/>
+      <c r="W14" s="7"/>
+      <c r="AC14" s="6"/>
+      <c r="AD14" s="12"/>
+      <c r="AE14" s="13"/>
+    </row>
+    <row r="15" ht="15.6" spans="1:29">
       <c r="A15" s="6"/>
       <c r="B15" s="6"/>
       <c r="C15" s="7"/>
@@ -1192,14 +1866,15 @@
       <c r="I15" s="6"/>
       <c r="J15" s="6"/>
       <c r="K15" s="6"/>
-      <c r="M15" s="6"/>
+      <c r="L15" s="6"/>
       <c r="N15" s="6"/>
       <c r="O15" s="6"/>
       <c r="P15" s="6"/>
-      <c r="V15" s="7"/>
-      <c r="AB15" s="6"/>
-    </row>
-    <row r="16" spans="1:35" ht="15.75">
+      <c r="Q15" s="6"/>
+      <c r="W15" s="7"/>
+      <c r="AC15" s="6"/>
+    </row>
+    <row r="16" ht="15.6" spans="1:29">
       <c r="A16" s="6"/>
       <c r="B16" s="6"/>
       <c r="C16" s="7"/>
@@ -1211,14 +1886,15 @@
       <c r="I16" s="6"/>
       <c r="J16" s="6"/>
       <c r="K16" s="6"/>
-      <c r="M16" s="6"/>
+      <c r="L16" s="6"/>
       <c r="N16" s="6"/>
       <c r="O16" s="6"/>
       <c r="P16" s="6"/>
-      <c r="V16" s="7"/>
-      <c r="AB16" s="6"/>
-    </row>
-    <row r="17" spans="1:28" ht="15.75">
+      <c r="Q16" s="6"/>
+      <c r="W16" s="7"/>
+      <c r="AC16" s="6"/>
+    </row>
+    <row r="17" ht="15.6" spans="1:29">
       <c r="A17" s="6"/>
       <c r="B17" s="6"/>
       <c r="C17" s="7"/>
@@ -1230,14 +1906,15 @@
       <c r="I17" s="6"/>
       <c r="J17" s="6"/>
       <c r="K17" s="6"/>
-      <c r="M17" s="6"/>
+      <c r="L17" s="6"/>
       <c r="N17" s="6"/>
       <c r="O17" s="6"/>
       <c r="P17" s="6"/>
-      <c r="V17" s="7"/>
-      <c r="AB17" s="6"/>
-    </row>
-    <row r="18" spans="1:28" ht="15.75">
+      <c r="Q17" s="6"/>
+      <c r="W17" s="7"/>
+      <c r="AC17" s="6"/>
+    </row>
+    <row r="18" ht="15.6" spans="1:29">
       <c r="A18" s="6"/>
       <c r="B18" s="6"/>
       <c r="C18" s="7"/>
@@ -1249,14 +1926,15 @@
       <c r="I18" s="6"/>
       <c r="J18" s="6"/>
       <c r="K18" s="6"/>
-      <c r="M18" s="6"/>
+      <c r="L18" s="6"/>
       <c r="N18" s="6"/>
       <c r="O18" s="6"/>
       <c r="P18" s="6"/>
-      <c r="V18" s="7"/>
-      <c r="AB18" s="6"/>
-    </row>
-    <row r="19" spans="1:28" ht="15.75">
+      <c r="Q18" s="6"/>
+      <c r="W18" s="7"/>
+      <c r="AC18" s="6"/>
+    </row>
+    <row r="19" ht="15.6" spans="1:28">
       <c r="A19" s="6"/>
       <c r="B19" s="6"/>
       <c r="C19" s="7"/>
@@ -1268,14 +1946,15 @@
       <c r="I19" s="6"/>
       <c r="J19" s="6"/>
       <c r="K19" s="6"/>
-      <c r="M19" s="6"/>
+      <c r="L19" s="6"/>
       <c r="N19" s="6"/>
       <c r="O19" s="6"/>
       <c r="P19" s="6"/>
-      <c r="V19" s="7"/>
-      <c r="AA19" s="6"/>
-    </row>
-    <row r="20" spans="1:28" ht="15.75">
+      <c r="Q19" s="6"/>
+      <c r="W19" s="7"/>
+      <c r="AB19" s="6"/>
+    </row>
+    <row r="20" ht="15.6" spans="1:23">
       <c r="A20" s="6"/>
       <c r="B20" s="6"/>
       <c r="C20" s="7"/>
@@ -1287,13 +1966,14 @@
       <c r="I20" s="6"/>
       <c r="J20" s="6"/>
       <c r="K20" s="6"/>
-      <c r="M20" s="6"/>
+      <c r="L20" s="6"/>
       <c r="N20" s="6"/>
       <c r="O20" s="6"/>
       <c r="P20" s="6"/>
-      <c r="V20" s="7"/>
-    </row>
-    <row r="21" spans="1:28" ht="15.75">
+      <c r="Q20" s="6"/>
+      <c r="W20" s="7"/>
+    </row>
+    <row r="21" ht="15.6" spans="1:23">
       <c r="A21" s="6"/>
       <c r="B21" s="6"/>
       <c r="C21" s="7"/>
@@ -1305,14 +1985,15 @@
       <c r="I21" s="6"/>
       <c r="J21" s="6"/>
       <c r="K21" s="6"/>
-      <c r="M21" s="6"/>
+      <c r="L21" s="6"/>
       <c r="N21" s="6"/>
       <c r="O21" s="6"/>
       <c r="P21" s="6"/>
       <c r="Q21" s="6"/>
-      <c r="V21" s="7"/>
-    </row>
-    <row r="22" spans="1:28" ht="15.75">
+      <c r="R21" s="6"/>
+      <c r="W21" s="7"/>
+    </row>
+    <row r="22" ht="15.6" spans="1:23">
       <c r="A22" s="6"/>
       <c r="B22" s="6"/>
       <c r="C22" s="7"/>
@@ -1324,14 +2005,15 @@
       <c r="I22" s="6"/>
       <c r="J22" s="6"/>
       <c r="K22" s="6"/>
-      <c r="M22" s="6"/>
+      <c r="L22" s="6"/>
       <c r="N22" s="6"/>
       <c r="O22" s="6"/>
       <c r="P22" s="6"/>
       <c r="Q22" s="6"/>
-      <c r="V22" s="6"/>
-    </row>
-    <row r="23" spans="1:28" ht="15.75">
+      <c r="R22" s="6"/>
+      <c r="W22" s="6"/>
+    </row>
+    <row r="23" ht="15.6" spans="1:24">
       <c r="A23" s="6"/>
       <c r="B23" s="6"/>
       <c r="C23" s="7"/>
@@ -1343,15 +2025,16 @@
       <c r="I23" s="6"/>
       <c r="J23" s="6"/>
       <c r="K23" s="6"/>
-      <c r="M23" s="6"/>
+      <c r="L23" s="6"/>
       <c r="N23" s="6"/>
       <c r="O23" s="6"/>
       <c r="P23" s="6"/>
       <c r="Q23" s="6"/>
-      <c r="V23" s="6"/>
+      <c r="R23" s="6"/>
       <c r="W23" s="6"/>
-    </row>
-    <row r="24" spans="1:28" ht="15.75">
+      <c r="X23" s="6"/>
+    </row>
+    <row r="24" ht="15.6" spans="1:24">
       <c r="A24" s="6"/>
       <c r="B24" s="6"/>
       <c r="C24" s="7"/>
@@ -1363,15 +2046,16 @@
       <c r="I24" s="6"/>
       <c r="J24" s="6"/>
       <c r="K24" s="6"/>
-      <c r="M24" s="6"/>
+      <c r="L24" s="6"/>
       <c r="N24" s="6"/>
       <c r="O24" s="6"/>
       <c r="P24" s="6"/>
       <c r="Q24" s="6"/>
-      <c r="V24" s="6"/>
+      <c r="R24" s="6"/>
       <c r="W24" s="6"/>
-    </row>
-    <row r="25" spans="1:28" ht="15.75">
+      <c r="X24" s="6"/>
+    </row>
+    <row r="25" ht="15.6" spans="1:28">
       <c r="A25" s="5"/>
       <c r="D25" s="6"/>
       <c r="E25" s="6"/>
@@ -1381,12 +2065,13 @@
       <c r="I25" s="6"/>
       <c r="J25" s="6"/>
       <c r="K25" s="6"/>
-      <c r="M25" s="6"/>
+      <c r="L25" s="6"/>
       <c r="N25" s="6"/>
       <c r="O25" s="6"/>
-      <c r="AA25" s="6"/>
-    </row>
-    <row r="26" spans="1:28" ht="15.75">
+      <c r="P25" s="6"/>
+      <c r="AB25" s="6"/>
+    </row>
+    <row r="26" ht="15.6" spans="1:16">
       <c r="A26" s="5"/>
       <c r="D26" s="6"/>
       <c r="E26" s="6"/>
@@ -1396,11 +2081,12 @@
       <c r="I26" s="6"/>
       <c r="J26" s="6"/>
       <c r="K26" s="6"/>
-      <c r="M26" s="6"/>
+      <c r="L26" s="6"/>
       <c r="N26" s="6"/>
       <c r="O26" s="6"/>
-    </row>
-    <row r="27" spans="1:28" ht="15.75">
+      <c r="P26" s="6"/>
+    </row>
+    <row r="27" ht="15.6" spans="4:16">
       <c r="D27" s="6"/>
       <c r="E27" s="6"/>
       <c r="F27" s="6"/>
@@ -1409,283 +2095,284 @@
       <c r="I27" s="6"/>
       <c r="J27" s="6"/>
       <c r="K27" s="6"/>
-      <c r="M27" s="6"/>
+      <c r="L27" s="6"/>
       <c r="N27" s="6"/>
       <c r="O27" s="6"/>
-    </row>
-    <row r="28" spans="1:28" ht="15.75">
+      <c r="P27" s="6"/>
+    </row>
+    <row r="28" ht="15.6" spans="4:16">
       <c r="D28" s="6"/>
       <c r="E28" s="6"/>
       <c r="F28" s="6"/>
-      <c r="O28" s="6"/>
-    </row>
-    <row r="29" spans="1:28" ht="15.75">
+      <c r="P28" s="6"/>
+    </row>
+    <row r="29" ht="15.6" spans="5:16">
       <c r="E29" s="6"/>
       <c r="F29" s="6"/>
-      <c r="O29" s="6"/>
-    </row>
-    <row r="30" spans="1:28" ht="15.75">
+      <c r="P29" s="6"/>
+    </row>
+    <row r="30" ht="15.6" spans="5:16">
       <c r="E30" s="6"/>
       <c r="F30" s="6"/>
-      <c r="O30" s="6"/>
-    </row>
-    <row r="31" spans="1:28" ht="15.75">
+      <c r="P30" s="6"/>
+    </row>
+    <row r="31" ht="15.6" spans="5:6">
       <c r="E31" s="6"/>
       <c r="F31" s="6"/>
     </row>
-    <row r="32" spans="1:28" ht="15.75">
+    <row r="32" ht="15.6" spans="6:6">
       <c r="F32" s="6"/>
     </row>
-    <row r="33" spans="6:6" ht="15.75">
+    <row r="33" ht="15.6" spans="6:6">
       <c r="F33" s="6"/>
     </row>
-    <row r="34" spans="6:6" ht="15.75">
+    <row r="34" ht="15.6" spans="6:6">
       <c r="F34" s="6"/>
     </row>
-    <row r="35" spans="6:6" ht="15.75">
+    <row r="35" ht="15.6" spans="6:6">
       <c r="F35" s="6"/>
     </row>
-    <row r="36" spans="6:6" ht="15.75">
+    <row r="36" ht="15.6" spans="6:6">
       <c r="F36" s="6"/>
     </row>
-    <row r="37" spans="6:6" ht="15.75">
+    <row r="37" ht="15.6" spans="6:6">
       <c r="F37" s="6"/>
     </row>
-    <row r="38" spans="6:6" ht="15.75">
+    <row r="38" ht="15.6" spans="6:6">
       <c r="F38" s="6"/>
     </row>
-    <row r="39" spans="6:6" ht="15.75">
+    <row r="39" ht="15.6" spans="6:6">
       <c r="F39" s="6"/>
     </row>
-    <row r="40" spans="6:6" ht="15.75">
+    <row r="40" ht="15.6" spans="6:6">
       <c r="F40" s="6"/>
     </row>
-    <row r="41" spans="6:6" ht="15.75">
+    <row r="41" ht="15.6" spans="6:6">
       <c r="F41" s="6"/>
     </row>
-    <row r="42" spans="6:6" ht="15.75">
+    <row r="42" ht="15.6" spans="6:6">
       <c r="F42" s="6"/>
     </row>
-    <row r="43" spans="6:6" ht="15.75">
+    <row r="43" ht="15.6" spans="6:6">
       <c r="F43" s="6"/>
     </row>
-    <row r="44" spans="6:6" ht="15.75">
+    <row r="44" ht="15.6" spans="6:6">
       <c r="F44" s="6"/>
     </row>
-    <row r="45" spans="6:6" ht="15.75">
+    <row r="45" ht="15.6" spans="6:6">
       <c r="F45" s="6"/>
     </row>
-    <row r="46" spans="6:6" ht="15.75">
+    <row r="46" ht="15.6" spans="6:6">
       <c r="F46" s="6"/>
     </row>
-    <row r="47" spans="6:6" ht="15.75">
+    <row r="47" ht="15.6" spans="6:6">
       <c r="F47" s="6"/>
     </row>
-    <row r="48" spans="6:6" ht="15.75">
+    <row r="48" ht="15.6" spans="6:6">
       <c r="F48" s="6"/>
     </row>
-    <row r="49" spans="6:6" ht="15.75">
+    <row r="49" ht="15.6" spans="6:6">
       <c r="F49" s="6"/>
     </row>
-    <row r="50" spans="6:6" ht="15.75">
+    <row r="50" ht="15.6" spans="6:6">
       <c r="F50" s="6"/>
     </row>
-    <row r="51" spans="6:6" ht="15.75">
+    <row r="51" ht="15.6" spans="6:6">
       <c r="F51" s="6"/>
     </row>
-    <row r="52" spans="6:6" ht="15.75">
+    <row r="52" ht="15.6" spans="6:6">
       <c r="F52" s="6"/>
     </row>
-    <row r="53" spans="6:6" ht="15.75">
+    <row r="53" ht="15.6" spans="6:6">
       <c r="F53" s="6"/>
     </row>
-    <row r="54" spans="6:6" ht="15.75">
+    <row r="54" ht="15.6" spans="6:6">
       <c r="F54" s="6"/>
     </row>
-    <row r="55" spans="6:6" ht="15.75">
+    <row r="55" ht="15.6" spans="6:6">
       <c r="F55" s="6"/>
     </row>
-    <row r="56" spans="6:6" ht="15.75">
+    <row r="56" ht="15.6" spans="6:6">
       <c r="F56" s="6"/>
     </row>
-    <row r="57" spans="6:6" ht="15.75">
+    <row r="57" ht="15.6" spans="6:6">
       <c r="F57" s="6"/>
     </row>
-    <row r="58" spans="6:6" ht="15.75">
+    <row r="58" ht="15.6" spans="6:6">
       <c r="F58" s="6"/>
     </row>
-    <row r="59" spans="6:6" ht="15.75">
+    <row r="59" ht="15.6" spans="6:6">
       <c r="F59" s="6"/>
     </row>
-    <row r="60" spans="6:6" ht="15.75">
+    <row r="60" ht="15.6" spans="6:6">
       <c r="F60" s="6"/>
     </row>
-    <row r="61" spans="6:6" ht="15.75">
+    <row r="61" ht="15.6" spans="6:6">
       <c r="F61" s="6"/>
     </row>
-    <row r="62" spans="6:6" ht="15.75">
+    <row r="62" ht="15.6" spans="6:6">
       <c r="F62" s="6"/>
     </row>
-    <row r="63" spans="6:6" ht="15.75">
+    <row r="63" ht="15.6" spans="6:6">
       <c r="F63" s="6"/>
     </row>
-    <row r="64" spans="6:6" ht="15.75">
+    <row r="64" ht="15.6" spans="6:6">
       <c r="F64" s="6"/>
     </row>
-    <row r="65" spans="6:6" ht="15.75">
+    <row r="65" ht="15.6" spans="6:6">
       <c r="F65" s="6"/>
     </row>
-    <row r="66" spans="6:6" ht="15.75">
+    <row r="66" ht="15.6" spans="6:6">
       <c r="F66" s="6"/>
     </row>
-    <row r="67" spans="6:6" ht="15.75">
+    <row r="67" ht="15.6" spans="6:6">
       <c r="F67" s="6"/>
     </row>
-    <row r="68" spans="6:6" ht="15.75">
+    <row r="68" ht="15.6" spans="6:6">
       <c r="F68" s="6"/>
     </row>
-    <row r="69" spans="6:6" ht="15.75">
+    <row r="69" ht="15.6" spans="6:6">
       <c r="F69" s="6"/>
     </row>
-    <row r="70" spans="6:6" ht="15.75">
+    <row r="70" ht="15.6" spans="6:6">
       <c r="F70" s="6"/>
     </row>
-    <row r="71" spans="6:6" ht="15.75">
+    <row r="71" ht="15.6" spans="6:6">
       <c r="F71" s="6"/>
     </row>
-    <row r="72" spans="6:6" ht="15.75">
+    <row r="72" ht="15.6" spans="6:6">
       <c r="F72" s="6"/>
     </row>
-    <row r="73" spans="6:6" ht="15.75">
+    <row r="73" ht="15.6" spans="6:6">
       <c r="F73" s="6"/>
     </row>
-    <row r="74" spans="6:6" ht="15.75">
+    <row r="74" ht="15.6" spans="6:6">
       <c r="F74" s="6"/>
     </row>
-    <row r="75" spans="6:6" ht="15.75">
+    <row r="75" ht="15.6" spans="6:6">
       <c r="F75" s="6"/>
     </row>
-    <row r="76" spans="6:6" ht="15.75">
+    <row r="76" ht="15.6" spans="6:6">
       <c r="F76" s="6"/>
     </row>
-    <row r="77" spans="6:6" ht="15.75">
+    <row r="77" ht="15.6" spans="6:6">
       <c r="F77" s="6"/>
     </row>
-    <row r="78" spans="6:6" ht="15.75">
+    <row r="78" ht="15.6" spans="6:6">
       <c r="F78" s="6"/>
     </row>
-    <row r="79" spans="6:6" ht="15.75">
+    <row r="79" ht="15.6" spans="6:6">
       <c r="F79" s="6"/>
     </row>
-    <row r="80" spans="6:6" ht="15.75">
+    <row r="80" ht="15.6" spans="6:6">
       <c r="F80" s="6"/>
     </row>
-    <row r="81" spans="6:6" ht="15.75">
+    <row r="81" ht="15.6" spans="6:6">
       <c r="F81" s="6"/>
     </row>
-    <row r="82" spans="6:6" ht="15.75">
+    <row r="82" ht="15.6" spans="6:6">
       <c r="F82" s="6"/>
     </row>
-    <row r="83" spans="6:6" ht="15.75">
+    <row r="83" ht="15.6" spans="6:6">
       <c r="F83" s="6"/>
     </row>
-    <row r="84" spans="6:6" ht="15.75">
+    <row r="84" ht="15.6" spans="6:6">
       <c r="F84" s="6"/>
     </row>
-    <row r="85" spans="6:6" ht="15.75">
+    <row r="85" ht="15.6" spans="6:6">
       <c r="F85" s="6"/>
     </row>
-    <row r="86" spans="6:6" ht="15.75">
+    <row r="86" ht="15.6" spans="6:6">
       <c r="F86" s="6"/>
     </row>
-    <row r="87" spans="6:6" ht="15.75">
+    <row r="87" ht="15.6" spans="6:6">
       <c r="F87" s="6"/>
     </row>
-    <row r="88" spans="6:6" ht="15.75">
+    <row r="88" ht="15.6" spans="6:6">
       <c r="F88" s="6"/>
     </row>
-    <row r="89" spans="6:6" ht="15.75">
+    <row r="89" ht="15.6" spans="6:6">
       <c r="F89" s="6"/>
     </row>
-    <row r="90" spans="6:6" ht="15.75">
+    <row r="90" ht="15.6" spans="6:6">
       <c r="F90" s="6"/>
     </row>
-    <row r="91" spans="6:6" ht="15.75">
+    <row r="91" ht="15.6" spans="6:6">
       <c r="F91" s="6"/>
     </row>
-    <row r="92" spans="6:6" ht="15.75">
+    <row r="92" ht="15.6" spans="6:6">
       <c r="F92" s="6"/>
     </row>
-    <row r="93" spans="6:6" ht="15.75">
+    <row r="93" ht="15.6" spans="6:6">
       <c r="F93" s="6"/>
     </row>
-    <row r="94" spans="6:6" ht="15.75">
+    <row r="94" ht="15.6" spans="6:6">
       <c r="F94" s="6"/>
     </row>
-    <row r="95" spans="6:6" ht="15.75">
+    <row r="95" ht="15.6" spans="6:6">
       <c r="F95" s="6"/>
     </row>
-    <row r="96" spans="6:6" ht="15.75">
+    <row r="96" ht="15.6" spans="6:6">
       <c r="F96" s="6"/>
     </row>
-    <row r="97" spans="6:6" ht="15.75">
+    <row r="97" ht="15.6" spans="6:6">
       <c r="F97" s="6"/>
     </row>
-    <row r="98" spans="6:6" ht="15.75">
+    <row r="98" ht="15.6" spans="6:6">
       <c r="F98" s="6"/>
     </row>
-    <row r="99" spans="6:6" ht="15.75">
+    <row r="99" ht="15.6" spans="6:6">
       <c r="F99" s="6"/>
     </row>
-    <row r="100" spans="6:6" ht="15.75">
+    <row r="100" ht="15.6" spans="6:6">
       <c r="F100" s="6"/>
     </row>
-    <row r="101" spans="6:6" ht="15.75">
+    <row r="101" ht="15.6" spans="6:6">
       <c r="F101" s="6"/>
     </row>
-    <row r="102" spans="6:6" ht="15.75">
+    <row r="102" ht="15.6" spans="6:6">
       <c r="F102" s="6"/>
     </row>
-    <row r="103" spans="6:6" ht="15.75">
+    <row r="103" ht="15.6" spans="6:6">
       <c r="F103" s="6"/>
     </row>
-    <row r="104" spans="6:6" ht="15.75">
+    <row r="104" ht="15.6" spans="6:6">
       <c r="F104" s="6"/>
     </row>
-    <row r="105" spans="6:6" ht="15.75">
+    <row r="105" ht="15.6" spans="6:6">
       <c r="F105" s="6"/>
     </row>
-    <row r="106" spans="6:6" ht="15.75">
+    <row r="106" ht="15.6" spans="6:6">
       <c r="F106" s="6"/>
     </row>
-    <row r="107" spans="6:6" ht="15.75">
+    <row r="107" ht="15.6" spans="6:6">
       <c r="F107" s="6"/>
     </row>
-    <row r="108" spans="6:6" ht="15.75">
+    <row r="108" ht="15.6" spans="6:6">
       <c r="F108" s="6"/>
     </row>
-    <row r="109" spans="6:6" ht="15.75">
+    <row r="109" ht="15.6" spans="6:6">
       <c r="F109" s="6"/>
     </row>
-    <row r="110" spans="6:6" ht="15.75">
+    <row r="110" ht="15.6" spans="6:6">
       <c r="F110" s="6"/>
     </row>
-    <row r="111" spans="6:6" ht="15.75">
+    <row r="111" ht="15.6" spans="6:6">
       <c r="F111" s="6"/>
     </row>
-    <row r="112" spans="6:6" ht="15.75">
+    <row r="112" ht="15.6" spans="6:6">
       <c r="F112" s="6"/>
     </row>
-    <row r="113" spans="6:6" ht="15.75">
+    <row r="113" ht="15.6" spans="6:6">
       <c r="F113" s="6"/>
     </row>
-    <row r="114" spans="6:6" ht="15.75">
+    <row r="114" ht="15.6" spans="6:6">
       <c r="F114" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
-  <drawing r:id="rId2"/>
-  <legacyDrawing r:id="rId3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>